--- a/PICHINCHA/Agosto/PICHINCHA-Agosto.xlsx
+++ b/PICHINCHA/Agosto/PICHINCHA-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F22CCDB-0CED-4160-8140-16E0C9EE0E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F659E15-2123-4C25-BC28-6172747877E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -247,15 +247,6 @@
     <t>ARBA</t>
   </si>
   <si>
-    <t>Vto. 14/08</t>
-  </si>
-  <si>
-    <t>Liquidacion mes de JULIO</t>
-  </si>
-  <si>
-    <t>TSG - MES DE JULIO</t>
-  </si>
-  <si>
     <t>ARTICULOS DE LIMPIEZA</t>
   </si>
   <si>
@@ -263,6 +254,15 @@
   </si>
   <si>
     <t>EDESUR</t>
+  </si>
+  <si>
+    <t>Vto. 15/09</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>TSG - MES DE AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -275,7 +275,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +376,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1084,7 +1091,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1289,6 +1296,7 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1352,7 +1360,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1721,22 +1730,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1744,27 +1753,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1772,13 +1781,13 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1786,29 +1795,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="122" t="s">
+      <c r="E11" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="122"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="123"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="143">
+      <c r="C12" s="122">
         <v>33631.699999999997</v>
       </c>
       <c r="D12" s="5"/>
@@ -1819,11 +1828,11 @@
         <v>-537107.59759646724</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="143">
+      <c r="C13" s="144">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -1835,7 +1844,7 @@
         <v>564150.37439999986</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
         <v>19</v>
       </c>
@@ -1851,12 +1860,12 @@
       </c>
       <c r="F14" s="59">
         <f>-(C38)</f>
-        <v>-488303.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-488587.19999999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15" s="120">
         <v>55570.55</v>
@@ -1865,7 +1874,7 @@
       <c r="E15" s="58"/>
       <c r="F15" s="59"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="31" t="s">
         <v>71</v>
       </c>
@@ -1876,20 +1885,20 @@
       <c r="E16" s="58"/>
       <c r="F16" s="59"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="120">
-        <v>56349.64</v>
+        <v>75</v>
+      </c>
+      <c r="C17" s="145">
+        <v>56633.440000000002</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C18" s="120">
         <v>14560</v>
@@ -1898,7 +1907,7 @@
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="31" t="s">
         <v>72</v>
       </c>
@@ -1909,22 +1918,22 @@
       <c r="F19" s="59"/>
       <c r="H19" s="108"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="32"/>
       <c r="B20" s="33"/>
       <c r="C20" s="87">
         <f>SUM(C12:C19)</f>
-        <v>392190.25</v>
+        <v>392474.05</v>
       </c>
       <c r="E20" s="60" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="119">
         <f>SUM(F12:F19)</f>
-        <v>-461260.62319646741</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-461544.42319646734</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>21</v>
       </c>
@@ -1933,7 +1942,7 @@
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
         <v>66</v>
       </c>
@@ -1946,9 +1955,9 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C23" s="120">
         <v>27650</v>
@@ -1957,7 +1966,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="31"/>
       <c r="B24" s="35"/>
       <c r="C24" s="120"/>
@@ -1965,7 +1974,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="31"/>
       <c r="B25" s="35"/>
       <c r="C25" s="120"/>
@@ -1973,7 +1982,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="31" t="s">
         <v>60</v>
       </c>
@@ -1983,7 +1992,7 @@
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="32"/>
       <c r="B27" s="33"/>
       <c r="C27" s="109">
@@ -1995,20 +2004,20 @@
       <c r="F27" s="55"/>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
         <v>12</v>
       </c>
       <c r="B28" s="48"/>
       <c r="C28" s="49">
         <f>+C27+C20</f>
-        <v>488303.4</v>
+        <v>488587.19999999995</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="69" t="s">
         <v>24</v>
       </c>
@@ -2017,18 +2026,18 @@
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44"/>
       <c r="B31" s="29"/>
       <c r="C31" s="54"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="52"/>
       <c r="B32" s="51"/>
       <c r="C32" s="53">
@@ -2036,7 +2045,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="61"/>
       <c r="B33" s="62"/>
       <c r="C33" s="53">
@@ -2044,19 +2053,19 @@
       </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="78"/>
       <c r="B34" s="79"/>
       <c r="C34" s="81"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="78"/>
       <c r="B35" s="85"/>
       <c r="C35" s="86"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="78"/>
       <c r="B36" s="84"/>
       <c r="C36" s="81">
@@ -2064,7 +2073,7 @@
       </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="63" t="s">
         <v>23</v>
       </c>
@@ -2074,98 +2083,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>54</v>
       </c>
       <c r="C38" s="53">
         <f>C28-C26</f>
-        <v>488303.4</v>
+        <v>488587.19999999995</v>
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C39" s="77">
         <f>+C28</f>
-        <v>488303.4</v>
+        <v>488587.19999999995</v>
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="63" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="64"/>
       <c r="C40" s="65">
         <f>+C28+C37</f>
-        <v>488303.4</v>
+        <v>488587.19999999995</v>
       </c>
       <c r="E40" s="16"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="123"/>
-      <c r="C47" s="123"/>
-      <c r="D47" s="123"/>
-      <c r="E47" s="123"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="123"/>
-      <c r="C48" s="123"/>
-      <c r="D48" s="123"/>
-      <c r="E48" s="123"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="123"/>
-      <c r="C49" s="123"/>
-      <c r="D49" s="123"/>
-      <c r="E49" s="123"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="124"/>
+      <c r="C47" s="124"/>
+      <c r="D47" s="124"/>
+      <c r="E47" s="124"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="124"/>
+      <c r="C48" s="124"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="124"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="124"/>
+      <c r="C49" s="124"/>
+      <c r="D49" s="124"/>
+      <c r="E49" s="124"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="19"/>
       <c r="B61" s="18"/>
       <c r="C61" s="20"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -2191,25 +2200,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2230,10 +2239,10 @@
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de JULIO</v>
+        <v>Liquidacion mes de AGOSTO</v>
       </c>
       <c r="B2" s="73"/>
       <c r="C2" s="73"/>
@@ -2250,7 +2259,7 @@
       <c r="L2" s="114"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2291,7 +2300,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2319,13 +2328,13 @@
       </c>
       <c r="L4" s="66" t="str">
         <f>'detalle y gastos'!F7</f>
-        <v>Vto. 14/08</v>
+        <v>Vto. 15/09</v>
       </c>
       <c r="M4" s="66" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2371,7 +2380,7 @@
         <v>101567.10720000001</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2417,7 +2426,7 @@
         <v>101567.10720000001</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2463,7 +2472,7 @@
         <v>101567.10720000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2509,7 +2518,7 @@
         <v>101567.10720000001</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2555,7 +2564,7 @@
         <v>101567.10720000001</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2602,71 +2611,71 @@
         <v>507835.53600000008</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="124"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="124"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="125"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="125"/>
+      <c r="M11" s="125"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="125"/>
-      <c r="K13" s="125"/>
-      <c r="L13" s="125"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="125"/>
-      <c r="L14" s="125"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="125"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="125"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="125"/>
-      <c r="I16" s="125"/>
-      <c r="J16" s="125"/>
-      <c r="K16" s="125"/>
-      <c r="L16" s="125"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="126"/>
+      <c r="H16" s="126"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2682,68 +2691,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="131" t="s">
+    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="134" t="s">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137">
+      <c r="B2" s="136"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="138">
         <v>565</v>
       </c>
-      <c r="E2" s="138"/>
+      <c r="E2" s="139"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="139" t="s">
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="139" t="s">
+      <c r="C3" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="141" t="s">
+      <c r="D3" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="126" t="s">
+      <c r="E3" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="126" t="s">
+      <c r="F3" s="127" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="126" t="s">
+      <c r="G3" s="127" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="140"/>
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="141"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -2766,7 +2775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -2789,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -2812,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -2835,7 +2844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -2858,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -2881,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -2900,12 +2909,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="128"/>
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="130"/>
+    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="129"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="131"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>

--- a/PICHINCHA/Agosto/PICHINCHA-Agosto.xlsx
+++ b/PICHINCHA/Agosto/PICHINCHA-Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PICHINCHA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F659E15-2123-4C25-BC28-6172747877E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81332EE-3022-4848-BDD8-5B1DA5546EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
   <si>
     <t>UF</t>
   </si>
@@ -205,9 +205,6 @@
     <t>PICHINCHA  267 - LANUS OESTE</t>
   </si>
   <si>
-    <t xml:space="preserve">Honorarios Administracion </t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
@@ -247,9 +244,6 @@
     <t>ARBA</t>
   </si>
   <si>
-    <t>ARTICULOS DE LIMPIEZA</t>
-  </si>
-  <si>
     <t>FLOW - INTERNET CAMARA</t>
   </si>
   <si>
@@ -263,6 +257,12 @@
   </si>
   <si>
     <t>TSG - MES DE AGOSTO</t>
+  </si>
+  <si>
+    <t>SEGURO DE VIDA. SRA MONICA GOROSITO</t>
+  </si>
+  <si>
+    <t>SIN ABONAR POR FALTA DE PAGO DE EXPENSAS</t>
   </si>
 </sst>
 </file>
@@ -275,7 +275,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,13 +376,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1091,7 +1084,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1360,8 +1353,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1729,23 +1720,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1753,27 +1744,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1781,13 +1772,13 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1795,12 +1786,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
@@ -1812,27 +1803,27 @@
       </c>
       <c r="F11" s="123"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="108"/>
-      <c r="C12" s="122">
-        <v>33631.699999999997</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B12" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="122"/>
       <c r="D12" s="5"/>
       <c r="E12" s="56" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="57">
-        <v>-537107.59759646724</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-461260.62319646741</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="144">
+      <c r="C13" s="122">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -1841,99 +1832,98 @@
       </c>
       <c r="F13" s="59">
         <f>'prorrateo '!F10</f>
-        <v>564150.37439999986</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>195321.36000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="80">
-        <v>33600</v>
-      </c>
+      <c r="B14" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="80"/>
       <c r="D14" s="5"/>
       <c r="E14" s="58" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="59">
-        <f>-(C38)</f>
-        <v>-488587.19999999995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <f>-(C37)</f>
+        <v>-225072.19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="120">
-        <v>55570.55</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="120"/>
       <c r="D15" s="5"/>
       <c r="E15" s="58"/>
       <c r="F15" s="59"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="120">
-        <v>99374.86</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B16" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="120"/>
       <c r="D16" s="5"/>
       <c r="E16" s="58"/>
       <c r="F16" s="59"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="145">
+        <v>73</v>
+      </c>
+      <c r="C17" s="120">
         <v>56633.440000000002</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="120">
-        <v>14560</v>
-      </c>
+      <c r="C18" s="120"/>
       <c r="D18" s="5"/>
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="120">
-        <v>7017.5</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C19" s="120"/>
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
       <c r="H19" s="108"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="32"/>
       <c r="B20" s="33"/>
       <c r="C20" s="87">
         <f>SUM(C12:C19)</f>
-        <v>392474.05</v>
+        <v>148719.44</v>
       </c>
       <c r="E20" s="60" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="119">
         <f>SUM(F12:F19)</f>
-        <v>-461544.42319646734</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-491011.45319646742</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>21</v>
       </c>
@@ -1942,31 +1932,31 @@
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="35"/>
       <c r="C22" s="120">
-        <f>65203*5%+65203</f>
-        <v>68463.149999999994</v>
+        <v>71833</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
-        <v>73</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B23" s="35"/>
       <c r="C23" s="120">
-        <v>27650</v>
+        <v>4519.75</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="31"/>
       <c r="B24" s="35"/>
       <c r="C24" s="120"/>
@@ -1974,215 +1964,207 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="31"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="31" t="s">
+        <v>59</v>
+      </c>
       <c r="B25" s="35"/>
-      <c r="C25" s="120"/>
+      <c r="C25" s="112"/>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="112"/>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="32"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="109">
+        <f>SUM(C21:C25)</f>
+        <v>76352.75</v>
+      </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="109">
-        <f>SUM(C21:C26)</f>
-        <v>96113.15</v>
+      <c r="E26" s="5"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49">
+        <f>+C26+C20</f>
+        <v>225072.19</v>
       </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="49">
-        <f>+C27+C20</f>
-        <v>488587.19999999995</v>
-      </c>
-      <c r="D28" s="5"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="82"/>
+      <c r="C28" s="83"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="69" t="s">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="82"/>
-      <c r="C29" s="83"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="44"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="54"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="44"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="54"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="52"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="53">
+        <v>0</v>
+      </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="52"/>
-      <c r="B32" s="51"/>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
       <c r="C32" s="53">
         <v>0</v>
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="53">
-        <v>0</v>
-      </c>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="78"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="81"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="81"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="86"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="86"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="81">
+        <v>0</v>
+      </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="78"/>
-      <c r="B36" s="84"/>
-      <c r="C36" s="81">
-        <v>0</v>
-      </c>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="63" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="64"/>
-      <c r="C37" s="65">
-        <f>SUM(C32:C36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B36" s="64"/>
+      <c r="C36" s="65">
+        <f>SUM(C31:C35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="53">
-        <f>C28-C26</f>
-        <v>488587.19999999995</v>
+      <c r="C37" s="53">
+        <f>C27-C25</f>
+        <v>225072.19</v>
+      </c>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="77">
+        <f>+C27</f>
+        <v>225072.19</v>
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="77">
-        <f>+C28</f>
-        <v>488587.19999999995</v>
-      </c>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="63" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="65">
-        <f>+C28+C37</f>
-        <v>488587.19999999995</v>
-      </c>
-      <c r="E40" s="16"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="64"/>
+      <c r="C39" s="65">
+        <f>+C27+C36</f>
+        <v>225072.19</v>
+      </c>
+      <c r="E39" s="16"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="124"/>
+      <c r="C46" s="124"/>
+      <c r="D46" s="124"/>
+      <c r="E46" s="124"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B47" s="124"/>
       <c r="C47" s="124"/>
       <c r="D47" s="124"/>
       <c r="E47" s="124"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="124"/>
       <c r="C48" s="124"/>
       <c r="D48" s="124"/>
       <c r="E48" s="124"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="124"/>
-      <c r="C49" s="124"/>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="19"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="20"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="18"/>
       <c r="B61" s="18"/>
-      <c r="C61" s="20"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C61" s="18"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B47:E49"/>
+    <mergeCell ref="B46:E48"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2200,25 +2182,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2239,7 +2221,7 @@
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de AGOSTO</v>
@@ -2259,7 +2241,7 @@
       <c r="L2" s="114"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2294,13 +2276,13 @@
         <v>38</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2331,10 +2313,10 @@
         <v>Vto. 15/09</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2342,23 +2324,20 @@
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="41">
-        <v>114593.04479999999</v>
-      </c>
-      <c r="F5" s="80">
-        <f>E5</f>
-        <v>114593.04479999999</v>
-      </c>
+        <v>97660.680000000008</v>
+      </c>
+      <c r="F5" s="80"/>
       <c r="G5" s="67">
         <f>E5-F5</f>
-        <v>0</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="H5" s="70">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>0</v>
+        <v>3906.4272000000005</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2373,14 +2352,14 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>97660.680000000008</v>
+        <v>199227.78720000002</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>101567.10720000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>207196.89868800002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2388,15 +2367,15 @@
         <v>2</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="41">
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="F6" s="80">
         <f>E6</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="G6" s="67">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
@@ -2426,7 +2405,7 @@
         <v>101567.10720000001</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2434,23 +2413,20 @@
         <v>3</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="41">
-        <v>114593.04479999999</v>
-      </c>
-      <c r="F7" s="80">
-        <f t="shared" ref="F7:F8" si="4">E7</f>
-        <v>114593.04479999999</v>
-      </c>
+        <v>97660.680000000008</v>
+      </c>
+      <c r="F7" s="80"/>
       <c r="G7" s="67">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="H7" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3906.4272000000005</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2465,14 +2441,14 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>97660.680000000008</v>
+        <v>199227.78720000002</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="3"/>
-        <v>101567.10720000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>207196.89868800002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2480,23 +2456,20 @@
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="41">
-        <v>114593.04479999999</v>
-      </c>
-      <c r="F8" s="80">
-        <f t="shared" si="4"/>
-        <v>114593.04479999999</v>
-      </c>
+        <v>97660.680000000008</v>
+      </c>
+      <c r="F8" s="80"/>
       <c r="G8" s="67">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="H8" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3906.4272000000005</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
@@ -2511,14 +2484,14 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>97660.680000000008</v>
+        <v>199227.78720000002</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="3"/>
-        <v>101567.10720000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>207196.89868800002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2526,15 +2499,15 @@
         <v>5</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="41">
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="F9" s="80">
         <f>E9</f>
-        <v>110185.62</v>
+        <v>97660.680000000008</v>
       </c>
       <c r="G9" s="67">
         <f t="shared" si="0"/>
@@ -2564,54 +2537,54 @@
         <v>101567.10720000001</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
       <c r="D10" s="45">
-        <f t="shared" ref="D10:M10" si="5">SUM(D5:D9)</f>
+        <f t="shared" ref="D10:M10" si="4">SUM(D5:D9)</f>
         <v>0</v>
       </c>
       <c r="E10" s="42">
-        <f t="shared" si="5"/>
-        <v>564150.37439999986</v>
+        <f t="shared" si="4"/>
+        <v>488303.4</v>
       </c>
       <c r="F10" s="42">
-        <f t="shared" si="5"/>
-        <v>564150.37439999986</v>
+        <f t="shared" si="4"/>
+        <v>195321.36000000002</v>
       </c>
       <c r="G10" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>292982.04000000004</v>
       </c>
       <c r="H10" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>11719.281600000002</v>
       </c>
       <c r="I10" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J10" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>488303.4</v>
       </c>
       <c r="K10" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L10" s="118">
-        <f t="shared" si="5"/>
-        <v>488303.4</v>
+        <f t="shared" si="4"/>
+        <v>793004.72160000016</v>
       </c>
       <c r="M10" s="118">
-        <f t="shared" si="5"/>
-        <v>507835.53600000008</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>824724.91046400007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="125"/>
       <c r="B11" s="125"/>
       <c r="C11" s="125"/>
@@ -2626,10 +2599,10 @@
       <c r="L11" s="125"/>
       <c r="M11" s="125"/>
     </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C13" s="126"/>
       <c r="D13" s="126"/>
       <c r="E13" s="126"/>
@@ -2641,7 +2614,7 @@
       <c r="K13" s="126"/>
       <c r="L13" s="126"/>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C14" s="126"/>
       <c r="D14" s="126"/>
       <c r="E14" s="126"/>
@@ -2653,7 +2626,7 @@
       <c r="K14" s="126"/>
       <c r="L14" s="126"/>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C15" s="126"/>
       <c r="D15" s="126"/>
       <c r="E15" s="126"/>
@@ -2665,7 +2638,7 @@
       <c r="K15" s="126"/>
       <c r="L15" s="126"/>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" s="126"/>
       <c r="D16" s="126"/>
       <c r="E16" s="126"/>
@@ -2691,12 +2664,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="132" t="s">
         <v>24</v>
       </c>
@@ -2707,7 +2680,7 @@
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="135" t="s">
         <v>50</v>
       </c>
@@ -2720,7 +2693,7 @@
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="140" t="s">
         <v>0</v>
       </c>
@@ -2743,7 +2716,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="141"/>
       <c r="B4" s="141"/>
       <c r="C4" s="141"/>
@@ -2752,7 +2725,7 @@
       <c r="F4" s="128"/>
       <c r="G4" s="128"/>
     </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -2775,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -2798,7 +2771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -2821,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -2844,7 +2817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -2867,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -2890,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -2909,7 +2882,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="129"/>
       <c r="B12" s="130"/>
       <c r="C12" s="130"/>

--- a/PICHINCHA/Agosto/PICHINCHA-Agosto.xlsx
+++ b/PICHINCHA/Agosto/PICHINCHA-Agosto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81332EE-3022-4848-BDD8-5B1DA5546EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3260621-E0DE-4BBE-A096-5D9937BAEEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
   <si>
     <t>UF</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>SIN ABONAR POR FALTA DE PAGO DE EXPENSAS</t>
+  </si>
+  <si>
+    <t>SERVISUR - BUSQUEDA Y REPARACION DE FUGA ELECTRICA - SELLADO CON SILICONA EN ARTEFACTOS DE ILUMINACION Y TOMAS CORRIENTE EN EXTERIOR</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1087,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1352,6 +1355,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1849,7 +1858,7 @@
       </c>
       <c r="F14" s="59">
         <f>-(C37)</f>
-        <v>-225072.19</v>
+        <v>-285072.19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1920,7 +1929,7 @@
       </c>
       <c r="F20" s="119">
         <f>SUM(F12:F19)</f>
-        <v>-491011.45319646742</v>
+        <v>-551011.45319646737</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1956,10 +1965,14 @@
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="120"/>
+    <row r="24" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="144" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="145"/>
+      <c r="C24" s="120">
+        <v>60000</v>
+      </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
@@ -1979,7 +1992,7 @@
       <c r="B26" s="33"/>
       <c r="C26" s="109">
         <f>SUM(C21:C25)</f>
-        <v>76352.75</v>
+        <v>136352.75</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1993,7 +2006,7 @@
       <c r="B27" s="48"/>
       <c r="C27" s="49">
         <f>+C26+C20</f>
-        <v>225072.19</v>
+        <v>285072.19</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
@@ -2071,7 +2084,7 @@
       </c>
       <c r="C37" s="53">
         <f>C27-C25</f>
-        <v>225072.19</v>
+        <v>285072.19</v>
       </c>
       <c r="F37" s="6"/>
     </row>
@@ -2081,7 +2094,7 @@
       </c>
       <c r="C38" s="77">
         <f>+C27</f>
-        <v>225072.19</v>
+        <v>285072.19</v>
       </c>
       <c r="F38" s="6"/>
     </row>
@@ -2092,7 +2105,7 @@
       <c r="B39" s="64"/>
       <c r="C39" s="65">
         <f>+C27+C36</f>
-        <v>225072.19</v>
+        <v>285072.19</v>
       </c>
       <c r="E39" s="16"/>
     </row>
@@ -2162,9 +2175,10 @@
       <c r="C67" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="B46:E48"/>
+    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
